--- a/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
+++ b/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2173" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2209" uniqueCount="394">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -806,7 +806,7 @@
     <t>ClinicalImpression.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -961,6 +961,22 @@
     <t>Investigation item for View resources so they can be approved.</t>
   </si>
   <si>
+    <t>ClinicalImpression.investigation.extension:otherItem</t>
+  </si>
+  <si>
+    <t>otherItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-clinicalimpression-otherItem}
+</t>
+  </si>
+  <si>
+    <t>Other item</t>
+  </si>
+  <si>
+    <t>Investigation item for Aggregated Triage resources so they can be approved.</t>
+  </si>
+  <si>
     <t>ClinicalImpression.investigation.modifierExtension</t>
   </si>
   <si>
@@ -1097,7 +1113,7 @@
     <t>Prognosis or outlook findings.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinicalimpression-prognosis</t>
+    <t>http://hl7.org/fhir/ValueSet/clinicalimpression-prognosis|4.0.1</t>
   </si>
   <si>
     <t>PRB-22</t>
@@ -1119,7 +1135,7 @@
     <t>ClinicalImpression.supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1157,7 +1173,7 @@
     <t>ClinicalImpression.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1528,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN60"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.9921875" customWidth="true" bestFit="true"/>
@@ -5777,11 +5793,13 @@
         <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="D38" t="s" s="2">
-        <v>303</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5794,26 +5812,22 @@
         <v>75</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -5861,7 +5875,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>306</v>
+        <v>179</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5870,7 +5884,7 @@
         <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>137</v>
@@ -5885,7 +5899,7 @@
         <v>75</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
@@ -5897,35 +5911,39 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>75</v>
+        <v>308</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -5949,11 +5967,13 @@
         <v>75</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>310</v>
+        <v>75</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -5971,19 +5991,19 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
@@ -5995,15 +6015,15 @@
         <v>75</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6011,10 +6031,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -6026,7 +6046,7 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>312</v>
+        <v>226</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>313</v>
@@ -6034,9 +6054,7 @@
       <c r="M40" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>315</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6061,13 +6079,11 @@
         <v>75</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>75</v>
+        <v>315</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>75</v>
@@ -6085,13 +6101,13 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>75</v>
@@ -6103,7 +6119,7 @@
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>316</v>
+        <v>75</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>75</v>
@@ -6114,10 +6130,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6140,7 +6156,7 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>100</v>
+        <v>317</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>318</v>
@@ -6148,7 +6164,9 @@
       <c r="M41" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N41" s="2"/>
+      <c r="N41" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
@@ -6197,7 +6215,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6215,7 +6233,7 @@
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>75</v>
+        <v>321</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -6226,10 +6244,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6240,7 +6258,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -6252,13 +6270,13 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>100</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6309,13 +6327,13 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
@@ -6327,7 +6345,7 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>323</v>
+        <v>75</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -6338,10 +6356,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6352,7 +6370,7 @@
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -6364,13 +6382,13 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>292</v>
+        <v>171</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6421,13 +6439,13 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
@@ -6439,7 +6457,7 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>75</v>
+        <v>328</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -6450,10 +6468,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6464,7 +6482,7 @@
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
@@ -6476,13 +6494,13 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>171</v>
+        <v>292</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>172</v>
+        <v>330</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>173</v>
+        <v>331</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6533,19 +6551,19 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>329</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>75</v>
@@ -6557,26 +6575,26 @@
         <v>75</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>175</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>199</v>
+        <v>75</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -6588,17 +6606,15 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>329</v>
+        <v>172</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6647,19 +6663,19 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
@@ -6676,14 +6692,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>303</v>
+        <v>199</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6696,26 +6712,24 @@
         <v>75</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>131</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>203</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -6763,7 +6777,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>306</v>
+        <v>179</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6787,47 +6801,51 @@
         <v>75</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>129</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>75</v>
+        <v>308</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -6851,11 +6869,13 @@
         <v>75</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>335</v>
+        <v>75</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -6873,39 +6893,39 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>323</v>
+        <v>75</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6928,13 +6948,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>337</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6961,13 +6981,11 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -6985,7 +7003,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7003,7 +7021,7 @@
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>75</v>
@@ -7014,10 +7032,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7040,13 +7058,13 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>171</v>
+        <v>342</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7097,7 +7115,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -7115,7 +7133,7 @@
         <v>75</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>75</v>
+        <v>328</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>75</v>
@@ -7126,10 +7144,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7140,7 +7158,7 @@
         <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -7152,13 +7170,13 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>226</v>
+        <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7185,13 +7203,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>345</v>
+        <v>75</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>346</v>
+        <v>75</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7209,13 +7227,13 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
@@ -7227,7 +7245,7 @@
         <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>347</v>
+        <v>75</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>75</v>
@@ -7238,10 +7256,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7264,13 +7282,13 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7297,13 +7315,13 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>75</v>
+        <v>351</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7321,7 +7339,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7339,7 +7357,7 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>75</v>
@@ -7350,10 +7368,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7376,13 +7394,13 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7433,7 +7451,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7462,10 +7480,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7488,17 +7506,15 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N53" t="s" s="2">
         <v>360</v>
       </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7547,7 +7563,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7562,7 +7578,7 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>361</v>
+        <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7576,10 +7592,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7590,7 +7606,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7602,15 +7618,17 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>171</v>
+        <v>362</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>172</v>
+        <v>363</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7659,22 +7677,22 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>174</v>
+        <v>361</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>75</v>
+        <v>366</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7683,26 +7701,26 @@
         <v>75</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>175</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>199</v>
+        <v>75</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7714,17 +7732,15 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>329</v>
+        <v>172</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7761,31 +7777,31 @@
         <v>75</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>178</v>
+        <v>75</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7802,21 +7818,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>75</v>
+        <v>199</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7825,19 +7841,19 @@
         <v>75</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>365</v>
+        <v>131</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>368</v>
+        <v>202</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7875,53 +7891,53 @@
         <v>75</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AC56" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="AD56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>370</v>
+        <v>135</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>371</v>
+        <v>179</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>372</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>75</v>
       </c>
@@ -7942,16 +7958,16 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7989,19 +8005,17 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>75</v>
+        <v>375</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8025,18 +8039,18 @@
         <v>75</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>75</v>
@@ -8058,16 +8072,16 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>171</v>
+        <v>380</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8117,7 +8131,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8141,17 +8155,19 @@
         <v>75</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>75</v>
       </c>
@@ -8172,15 +8188,17 @@
         <v>87</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>268</v>
+        <v>171</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8229,7 +8247,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8253,7 +8271,7 @@
         <v>75</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="60">
@@ -8269,7 +8287,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>86</v>
@@ -8284,13 +8302,13 @@
         <v>87</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8341,10 +8359,10 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>86</v>
@@ -8365,7 +8383,119 @@
         <v>75</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
         <v>388</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
+++ b/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
+++ b/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
+++ b/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
+++ b/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
+++ b/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
+++ b/fhir/StructureDefinition-ehealth-clinicalimpression.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
